--- a/assets/csv/alumni.xlsx
+++ b/assets/csv/alumni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F00C059-7300-1A4A-B6EE-1CB1EC0BA4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F5132-72D2-3E48-819B-3859C734EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -452,20 +452,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -795,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1650962B-F96C-FE4E-A26E-251242D6E0F9}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
@@ -883,10 +891,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="7"/>
@@ -1207,19 +1215,25 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="E28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
-      <c r="B29" s="6" t="s">
-        <v>36</v>
+      <c r="B29" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
@@ -1229,25 +1243,25 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
-      <c r="B30" s="9" t="s">
-        <v>37</v>
+      <c r="B30" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
@@ -1258,24 +1272,24 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
       <c r="B32" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3"/>
       <c r="B33" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
@@ -1286,38 +1300,38 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
       <c r="B34" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
       <c r="B35" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
       <c r="B36" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
@@ -1328,10 +1342,10 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
       <c r="B37" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
@@ -1341,144 +1355,138 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
-      <c r="B38" s="6" t="s">
-        <v>45</v>
+      <c r="B38" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
-      <c r="B39" s="9" t="s">
-        <v>46</v>
+      <c r="B39" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="4"/>
+      <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
       <c r="B42" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="F42" s="11"/>
+      <c r="E42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="10"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
       <c r="B43" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="F45" s="6"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
-      <c r="B46" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>90</v>
+      <c r="B46" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" s="6"/>
+      <c r="E46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
-      <c r="B47" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
@@ -1486,7 +1494,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="6"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
@@ -1494,7 +1502,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="12"/>
+      <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
@@ -1802,11 +1810,11 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="3"/>
@@ -1816,15 +1824,10 @@
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="3"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>